--- a/management_db.xlsx
+++ b/management_db.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,52 @@
         <is>
           <t>합계금액</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026. 01. 13.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>피복</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>정화빌딩</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>최재혁</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>회색동복</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>상의:100/하의:32/모자:중</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -480,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +549,26 @@
         <is>
           <t>총액</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>정화빌딩</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/management_db.xlsx
+++ b/management_db.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,52 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026. 01. 13.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>피복</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>정화빌딩</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>최재혁</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>회색동복</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>상의:100/하의:32/모자:중</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/management_db.xlsx
+++ b/management_db.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,6 +558,52 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026. 01. 13.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>경비물품</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>정화빌딩</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>최재혁</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">휴지 </t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>100M</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/management_db.xlsx
+++ b/management_db.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,6 +605,52 @@
       </c>
       <c r="J4" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026. 01. 14.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>피복</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>우장산꿈에그린</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>김솔휘</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>동계상의(회색동복)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>상의:100/하의:32/모자:중</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>19500</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19500</v>
       </c>
     </row>
   </sheetData>
@@ -618,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,10 +702,30 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>우장산꿈에그린</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>정화빌딩</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/management_db.xlsx
+++ b/management_db.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -650,6 +650,236 @@
         <v>19500</v>
       </c>
       <c r="J5" t="n">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026. 01. 13.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>피복</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>정화빌딩</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>강용석</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>회색동복</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>상의:100/하의:32/모자:중</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026. 01. 13.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>피복</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>정화빌딩</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>강용석</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>회색동복</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>상의:100/하의:32/모자:중</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026. 01. 13.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>피복</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>정화빌딩</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>강용석</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>회색동복</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>상의:100/하의:32/모자:중</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026. 01. 13.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>피복</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>정화빌딩</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>강용석</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>회색동복</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>상의:100/하의:32/모자:중</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026. 01. 14.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>피복</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>우장산꿈에그린</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>김솔휘</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>동계상의(회색동복)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>상의:100/하의:32/모자:중</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19500</v>
+      </c>
+      <c r="J10" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -706,7 +936,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19500</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="3">
